--- a/data/Terre di Pedemonte/investment_decision/Verscio_district_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Verscio_district_investment_decision.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -512,13 +512,13 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.787377573367231</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.852787610573972</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -549,13 +549,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>2.46013057823239</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5.852787610573972</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.79702191306353</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.852787610573972</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.994701352460634</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.852787610573972</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -660,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>3.123623802236492</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.852787610573972</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -680,7 +680,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1954745198777006</v>
+        <v>0.1792468466984948</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,19 +694,19 @@
         <v>5.852787610573972</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1954825773482623</v>
+        <v>0.1765373798355792</v>
       </c>
       <c r="G7" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.179237743802524</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.787377573367231</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.1954058025086572</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5.852787610573972</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.1954826240087507</v>
+        <v>0.1765106701435637</v>
       </c>
       <c r="K7" t="n">
         <v>1.787377573367231</v>
@@ -717,7 +717,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1997874190786948</v>
+        <v>0.242236601905776</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -731,19 +731,19 @@
         <v>5.852787610573972</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1997908162322364</v>
+        <v>0.2425770624360767</v>
       </c>
       <c r="G8" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2425433999764706</v>
+      </c>
+      <c r="I8" t="n">
         <v>2.46013057823239</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.1997163513009803</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.852787610573972</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.1997908359050162</v>
+        <v>0.242573639207032</v>
       </c>
       <c r="K8" t="n">
         <v>2.46013057823239</v>
@@ -754,7 +754,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2027184548985667</v>
+        <v>0.3134356899696006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -768,19 +768,19 @@
         <v>5.852787610573972</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2025216286842009</v>
+        <v>0.3152008843387248</v>
       </c>
       <c r="G9" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3036444335788492</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.79702191306353</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.2030504174785254</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5.852787610573972</v>
-      </c>
       <c r="J9" t="n">
-        <v>0.2028410572930903</v>
+        <v>0.3063119249036607</v>
       </c>
       <c r="K9" t="n">
         <v>2.79702191306353</v>
@@ -791,7 +791,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2048032893440261</v>
+        <v>0.327458900616087</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         <v>5.852787610573972</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2048316988609504</v>
+        <v>0.3312590179915986</v>
       </c>
       <c r="G10" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3139578293235294</v>
+      </c>
+      <c r="I10" t="n">
         <v>2.994701352460634</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.2048032893458611</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.852787610573972</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.2048316988609504</v>
+        <v>0.3163913939890953</v>
       </c>
       <c r="K10" t="n">
         <v>2.994701352460634</v>
@@ -828,7 +828,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.202706216164589</v>
+        <v>0.3259276857125549</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,19 +842,19 @@
         <v>5.852787610573972</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2027095804609316</v>
+        <v>0.3253573187422397</v>
       </c>
       <c r="G11" t="n">
+        <v>5.852787610573972</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3073658617071863</v>
+      </c>
+      <c r="I11" t="n">
         <v>3.123623802236492</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.2027062161645891</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5.852787610573972</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.2027095804609316</v>
+        <v>0.3095697706695742</v>
       </c>
       <c r="K11" t="n">
         <v>3.123623802236492</v>
@@ -1043,746 +1043,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.008207141374442783</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.008207509715954176</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.008204000009000798</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.008207511849005075</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.94321620687536</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.008404302480773947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.008404457779221565</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.008401053668078425</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.008404458678548641</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.94321620687536</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.008633599407189092</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.008634898127962773</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.008553468121909059</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.008634898127962773</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.94321620687536</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.008633599407189092</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.008634898127962773</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.008633599407272976</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.008634898127962773</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.94321620687536</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.008633599407189092</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.008634898127962773</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.008633599407272976</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.94321620687536</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.008634898127962773</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.94321620687536</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05482837885156375</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.05482837885156375</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.08652173441132684</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.08652173441132684</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1076949787876673</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.1076949787876673</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1232717461966999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.1232717461966999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.1355254623817148</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.6846108504035027</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.1355254623817148</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.1056932604367494</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.1056932604367494</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1667888856121963</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.1667888856121963</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.2076047783858646</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.2076047783858646</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.2376322818249637</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.2376322818249637</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.2612539033864382</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.319731759813981</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.2612539033864382</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.01462090102708367</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.01462090102708367</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.02307246250968716</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.02307246250968716</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.02871866101004461</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.02871866101004461</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.03287246565245331</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.03287246565245331</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Verscio</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.03614012330179062</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.182562893440934</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.03614012330179062</v>
       </c>
     </row>
   </sheetData>
